--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260709.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260709.xlsx
@@ -865,17 +865,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>台灣高鐵</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>2,678,000</t>
+          <t>84,199,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>台灣高鐵</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>84,199,000</t>
+          <t>2,678,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2,499,678</t>
+          <t>18,166,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>18,166,000</t>
+          <t>2,499,678</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>3,365,000</t>
+          <t>3,577,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>3,577,000</t>
+          <t>3,365,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>16,850,000</t>
+          <t>15,773,648</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>東和鋼鐵</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>15,280,000</t>
+          <t>16,850,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>東和鋼鐵</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>15,773,648</t>
+          <t>15,280,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
